--- a/artfynd/A 62638-2022 artfynd.xlsx
+++ b/artfynd/A 62638-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62638-2022 artfynd.xlsx
+++ b/artfynd/A 62638-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105311082</v>
+        <v>105314649</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2014</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582229.5146090231</v>
+        <v>582166</v>
       </c>
       <c r="R2" t="n">
-        <v>7083619.271610521</v>
+        <v>7083581</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105310166</v>
+        <v>105311080</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582269.3151280056</v>
+        <v>582279</v>
       </c>
       <c r="R3" t="n">
-        <v>7083633.987964195</v>
+        <v>7083639</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,19 +845,9 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105310167</v>
+        <v>105311081</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582251.9191429375</v>
+        <v>582255</v>
       </c>
       <c r="R4" t="n">
-        <v>7083640.588007313</v>
+        <v>7083656</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,21 +947,11 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1005,6 +960,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>På Björk</t>
+        </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1026,37 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105310168</v>
+        <v>105311082</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582255.0795214991</v>
+        <v>582230</v>
       </c>
       <c r="R5" t="n">
-        <v>7083654.783957332</v>
+        <v>7083619</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,21 +1054,11 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1122,11 +1067,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Flera ex, gamla blomstänglar</t>
-        </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -1148,37 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105311080</v>
+        <v>105310166</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582278.8966263519</v>
+        <v>582269</v>
       </c>
       <c r="R6" t="n">
-        <v>7083639.090807539</v>
+        <v>7083634</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,19 +1156,9 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,37 +1190,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105314649</v>
+        <v>105310167</v>
       </c>
       <c r="B7" t="n">
-        <v>90174</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2014</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Pers.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582166.0538942794</v>
+        <v>582252</v>
       </c>
       <c r="R7" t="n">
-        <v>7083580.560402533</v>
+        <v>7083641</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1338,19 +1258,9 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,37 +1292,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105311081</v>
+        <v>105310168</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582255.0563923658</v>
+        <v>582255</v>
       </c>
       <c r="R8" t="n">
-        <v>7083655.665412368</v>
+        <v>7083655</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1455,21 +1360,11 @@
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-10</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1481,7 +1376,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På Björk</t>
+          <t>Flera ex, gamla blomstänglar</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">

--- a/artfynd/A 62638-2022 artfynd.xlsx
+++ b/artfynd/A 62638-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314649</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311080</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311081</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311082</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310166</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310167</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,8 +1431,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310168</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>